--- a/boletines_excel/295 BOLETÍN DE VIA C (BUENURAQUI - HUALQUI) 22-10-26.xlsx
+++ b/boletines_excel/295 BOLETÍN DE VIA C (BUENURAQUI - HUALQUI) 22-10-26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F681AED4-69B6-49DB-8D1B-3552956DF17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887B77DC-E444-4EF8-85E3-FAD9470503AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$M$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$M$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="184">
   <si>
     <t>BLOCK</t>
   </si>
@@ -552,15 +552,6 @@
     <t>DEC#11 NOTIFIQUE A MAQUINISTA DE TRENES ELÉCTRICOS DEBE BAJAR PANTÓGRAFO AL INGRESO Y SALIDA DE VÍA LOCAL EN PATIO ELÉCTRICO UNIHUE</t>
   </si>
   <si>
-    <t>29 P. 3</t>
-  </si>
-  <si>
-    <t>29 P. 17</t>
-  </si>
-  <si>
-    <t>DEC#7314: “NOTIFIQUE A MAQUINAS ELÉCTRICAS BAJAR PANTÓGRAFO DESDE KM 29/3 AL KM 29/17”, POR SUSPENSOR CORTADO EN KM 29/9-10 (ESTACIÓN UNIHUE).</t>
-  </si>
-  <si>
     <t>QUILACOYA</t>
   </si>
   <si>
@@ -755,6 +746,9 @@
   </si>
   <si>
     <t>SR. RICARDO LAGOS HORMAZABAL.</t>
+  </si>
+  <si>
+    <t>295-A</t>
   </si>
 </sst>
 </file>
@@ -1872,6 +1866,117 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1881,9 +1986,6 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1955,114 +2057,6 @@
     </xf>
     <xf numFmtId="20" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2196,13 +2190,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>77320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>3207683</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>1704975</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2946,7 +2940,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
@@ -2966,44 +2960,44 @@
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
-      <c r="E1" s="135" t="s">
+      <c r="E1" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
       <c r="I1" s="22"/>
-      <c r="J1" s="129">
+      <c r="J1" s="128">
         <v>46317</v>
       </c>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="130"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="129"/>
     </row>
     <row r="2" spans="1:13" ht="13.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="131"/>
-      <c r="B2" s="132"/>
+      <c r="A2" s="130"/>
+      <c r="B2" s="131"/>
       <c r="C2" s="19"/>
       <c r="D2" s="16"/>
       <c r="E2" s="32"/>
       <c r="F2" s="72"/>
       <c r="G2" s="17"/>
       <c r="H2" s="73"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="134"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="133"/>
     </row>
     <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="137"/>
-      <c r="B3" s="138"/>
+      <c r="A3" s="136"/>
+      <c r="B3" s="137"/>
       <c r="C3" s="74"/>
       <c r="D3" s="75"/>
-      <c r="E3" s="136" t="s">
+      <c r="E3" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="136"/>
+      <c r="F3" s="135"/>
       <c r="G3" s="30" t="s">
         <v>21</v>
       </c>
@@ -3017,20 +3011,20 @@
       <c r="M3" s="23"/>
     </row>
     <row r="4" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="139"/>
-      <c r="B4" s="140"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
       <c r="C4" s="77"/>
       <c r="D4" s="78"/>
-      <c r="E4" s="147">
+      <c r="E4" s="127">
         <f ca="1">TODAY()</f>
         <v>46316</v>
       </c>
-      <c r="F4" s="147"/>
-      <c r="G4" s="31">
-        <v>295</v>
+      <c r="F4" s="127"/>
+      <c r="G4" s="31" t="s">
+        <v>183</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I4" s="79"/>
       <c r="J4" s="79"/>
@@ -3039,8 +3033,8 @@
       <c r="M4" s="24"/>
     </row>
     <row r="5" spans="1:13" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="141"/>
-      <c r="B5" s="142"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="124"/>
       <c r="C5" s="80"/>
       <c r="D5" s="81"/>
       <c r="E5" s="82"/>
@@ -3056,84 +3050,84 @@
     <row r="6" spans="1:13" s="47" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="83"/>
-      <c r="C6" s="148" t="s">
+      <c r="C6" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="148"/>
+      <c r="D6" s="101"/>
       <c r="E6" s="84"/>
-      <c r="F6" s="148" t="s">
+      <c r="F6" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="148"/>
+      <c r="G6" s="101"/>
       <c r="H6" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="148" t="s">
+      <c r="I6" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="148"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="148"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
       <c r="M6" s="46"/>
     </row>
     <row r="7" spans="1:13" s="49" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="44"/>
       <c r="B7" s="86"/>
-      <c r="C7" s="151" t="s">
+      <c r="C7" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="151"/>
+      <c r="D7" s="102"/>
       <c r="E7" s="87"/>
-      <c r="F7" s="151" t="s">
+      <c r="F7" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="151"/>
+      <c r="G7" s="102"/>
       <c r="H7" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="149" t="s">
+      <c r="I7" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="149"/>
-      <c r="K7" s="149"/>
-      <c r="L7" s="149"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
       <c r="M7" s="48"/>
     </row>
     <row r="8" spans="1:13" s="49" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="44"/>
       <c r="B8" s="86"/>
-      <c r="C8" s="149" t="s">
+      <c r="C8" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="149"/>
+      <c r="D8" s="103"/>
       <c r="E8" s="86"/>
-      <c r="F8" s="149" t="s">
+      <c r="F8" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="149"/>
+      <c r="G8" s="103"/>
       <c r="H8" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="150" t="s">
+      <c r="I8" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="150"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="150"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
       <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" s="49" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="44"/>
       <c r="B9" s="90"/>
-      <c r="C9" s="150" t="s">
+      <c r="C9" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="150"/>
+      <c r="D9" s="104"/>
       <c r="E9" s="91"/>
-      <c r="F9" s="150" t="s">
+      <c r="F9" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="164"/>
+      <c r="G9" s="105"/>
       <c r="H9" s="89"/>
       <c r="I9" s="92"/>
       <c r="J9" s="92"/>
@@ -3144,15 +3138,15 @@
     <row r="10" spans="1:13" s="47" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
       <c r="B10" s="45"/>
-      <c r="C10" s="148" t="s">
+      <c r="C10" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="148"/>
+      <c r="D10" s="101"/>
       <c r="E10" s="93"/>
-      <c r="F10" s="148" t="s">
+      <c r="F10" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="148"/>
+      <c r="G10" s="101"/>
       <c r="H10" s="85" t="s">
         <v>13</v>
       </c>
@@ -3165,15 +3159,15 @@
     <row r="11" spans="1:13" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
       <c r="B11" s="45"/>
-      <c r="C11" s="151" t="s">
+      <c r="C11" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="151"/>
+      <c r="D11" s="102"/>
       <c r="E11" s="93"/>
-      <c r="F11" s="151" t="s">
+      <c r="F11" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="151"/>
+      <c r="G11" s="102"/>
       <c r="H11" s="95" t="s">
         <v>14</v>
       </c>
@@ -3186,15 +3180,15 @@
     <row r="12" spans="1:13" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="44"/>
       <c r="B12" s="45"/>
-      <c r="C12" s="149" t="s">
+      <c r="C12" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="149"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="93"/>
-      <c r="F12" s="149" t="s">
+      <c r="F12" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="149"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="88" t="s">
         <v>34</v>
       </c>
@@ -3223,15 +3217,15 @@
       <c r="A14" s="39"/>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="104" t="s">
+      <c r="D14" s="110" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="110"/>
       <c r="K14" s="40"/>
       <c r="L14" s="40"/>
       <c r="M14" s="41"/>
@@ -3246,14 +3240,14 @@
       <c r="E15" s="66"/>
       <c r="F15" s="66"/>
       <c r="G15" s="64"/>
-      <c r="H15" s="111" t="s">
+      <c r="H15" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="112"/>
+      <c r="I15" s="147"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="148"/>
     </row>
     <row r="16" spans="1:13" ht="78.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="60"/>
@@ -3263,63 +3257,63 @@
       <c r="E16" s="62"/>
       <c r="F16" s="62"/>
       <c r="G16" s="63"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="114"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="150"/>
     </row>
     <row r="17" spans="1:13" s="47" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="105" t="s">
+      <c r="A17" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="106"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="107"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="142"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="142"/>
+      <c r="L17" s="142"/>
+      <c r="M17" s="143"/>
     </row>
     <row r="18" spans="1:13" s="47" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="110"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="145"/>
+      <c r="F18" s="145"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="145"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="146"/>
     </row>
     <row r="19" spans="1:13" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="103"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="139"/>
+      <c r="L19" s="139"/>
+      <c r="M19" s="140"/>
     </row>
     <row r="20" spans="1:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="50"/>
@@ -3340,69 +3334,69 @@
       <c r="A21" s="39"/>
       <c r="B21" s="40"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
       <c r="K21" s="40"/>
       <c r="L21" s="40"/>
       <c r="M21" s="41"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="159" t="s">
+      <c r="B22" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="160"/>
-      <c r="D22" s="145" t="s">
+      <c r="C22" s="115"/>
+      <c r="D22" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="115" t="s">
+      <c r="E22" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="116"/>
-      <c r="G22" s="145" t="s">
+      <c r="F22" s="152"/>
+      <c r="G22" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="145" t="s">
+      <c r="H22" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="I22" s="156" t="s">
+      <c r="I22" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="157"/>
-      <c r="K22" s="158" t="s">
+      <c r="J22" s="112"/>
+      <c r="K22" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="157"/>
-      <c r="M22" s="152" t="s">
+      <c r="L22" s="112"/>
+      <c r="M22" s="106" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="144"/>
+      <c r="A23" s="126"/>
       <c r="B23" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="146"/>
+      <c r="D23" s="117"/>
       <c r="E23" s="33" t="s">
         <v>1</v>
       </c>
       <c r="F23" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G23" s="146"/>
-      <c r="H23" s="146"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
       <c r="I23" s="14" t="s">
         <v>8</v>
       </c>
@@ -3415,7 +3409,7 @@
       <c r="L23" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="153"/>
+      <c r="M23" s="107"/>
     </row>
     <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="26" cm="1">
@@ -4047,7 +4041,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="26" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>16</v>
@@ -4056,22 +4050,22 @@
         <v>101</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E39" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F39" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="I39" s="12">
         <v>0</v>
@@ -4080,7 +4074,7 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K39" s="13">
-        <v>46310</v>
+        <v>44524</v>
       </c>
       <c r="L39" s="13" t="s">
         <v>65</v>
@@ -4089,31 +4083,31 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="26" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>17</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="34" t="s">
+      <c r="F40" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="F40" s="34" t="s">
+      <c r="G40" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>93</v>
-      </c>
       <c r="H40" s="10" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I40" s="12">
         <v>0</v>
@@ -4122,13 +4116,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K40" s="13">
-        <v>44524</v>
+        <v>41604</v>
       </c>
       <c r="L40" s="13" t="s">
         <v>65</v>
       </c>
       <c r="M40" s="27" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -4137,25 +4131,25 @@
         <v>18</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="E41" s="34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I41" s="12">
         <v>0</v>
@@ -4164,40 +4158,40 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K41" s="13">
-        <v>41604</v>
+        <v>43091</v>
       </c>
       <c r="L41" s="13" t="s">
         <v>65</v>
       </c>
       <c r="M41" s="27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="26" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>19</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F42" s="34" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I42" s="12">
         <v>0</v>
@@ -4206,13 +4200,13 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K42" s="13">
-        <v>43091</v>
+        <v>46275</v>
       </c>
       <c r="L42" s="13" t="s">
         <v>65</v>
       </c>
       <c r="M42" s="27" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4221,10 +4215,10 @@
         <v>20</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>54</v>
@@ -4239,7 +4233,7 @@
         <v>63</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I43" s="12">
         <v>0</v>
@@ -4257,31 +4251,31 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="26" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>21</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E44" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F44" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="F44" s="34" t="s">
+      <c r="G44" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="G44" s="10" t="s">
-        <v>63</v>
-      </c>
       <c r="H44" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I44" s="12">
         <v>0</v>
@@ -4290,139 +4284,139 @@
         <v>0.99930555555555556</v>
       </c>
       <c r="K44" s="13">
-        <v>46275</v>
+        <v>46308</v>
       </c>
       <c r="L44" s="13" t="s">
         <v>65</v>
       </c>
       <c r="M44" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="26" cm="1">
-        <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="39"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="110" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="110"/>
+      <c r="F45" s="110"/>
+      <c r="G45" s="110"/>
+      <c r="H45" s="110"/>
+      <c r="I45" s="110"/>
+      <c r="J45" s="110"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="41"/>
+    </row>
+    <row r="46" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="157" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="156"/>
+      <c r="D46" s="153" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="151" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="152"/>
+      <c r="G46" s="153" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="153" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="163" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="164"/>
+      <c r="K46" s="161" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="162"/>
+      <c r="M46" s="159" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="158"/>
+      <c r="B47" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="154"/>
+      <c r="E47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="154"/>
+      <c r="H47" s="154"/>
+      <c r="I47" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="160"/>
+    </row>
+    <row r="48" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" cm="1">
+        <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>22</v>
       </c>
-      <c r="B45" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="F45" s="34" t="s">
+      <c r="B48" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="E48" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="F48" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="I45" s="12">
-        <v>0</v>
-      </c>
-      <c r="J45" s="12">
-        <v>0.99930555555555556</v>
-      </c>
-      <c r="K45" s="13">
-        <v>46308</v>
-      </c>
-      <c r="L45" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M45" s="27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="39"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="40"/>
-      <c r="L46" s="40"/>
-      <c r="M46" s="41"/>
-    </row>
-    <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="121" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="120"/>
-      <c r="D47" s="117" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="115" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" s="116"/>
-      <c r="G47" s="117" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="117" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="127" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="128"/>
-      <c r="K47" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="126"/>
-      <c r="M47" s="123" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="122"/>
-      <c r="B48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="118"/>
-      <c r="E48" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="118"/>
-      <c r="H48" s="118"/>
-      <c r="I48" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="L48" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M48" s="124"/>
-    </row>
-    <row r="49" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="G48" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I48" s="37">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J48" s="37">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K48" s="13">
+        <v>46317</v>
+      </c>
+      <c r="L48" s="13">
+        <v>46317</v>
+      </c>
+      <c r="M48" s="27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="26" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>23</v>
@@ -4431,22 +4425,22 @@
         <v>53</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="D49" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="F49" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E49" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="F49" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>146</v>
-      </c>
       <c r="H49" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I49" s="37">
         <v>0.66666666666666663</v>
@@ -4461,7 +4455,7 @@
         <v>46317</v>
       </c>
       <c r="M49" s="27" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4476,25 +4470,25 @@
         <v>60</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="E50" s="34" t="s">
         <v>150</v>
       </c>
       <c r="F50" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H50" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="I50" s="37">
         <v>0.66666666666666663</v>
       </c>
       <c r="J50" s="37">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="K50" s="13">
         <v>46317</v>
@@ -4503,7 +4497,7 @@
         <v>46317</v>
       </c>
       <c r="M50" s="27" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4521,22 +4515,22 @@
         <v>67</v>
       </c>
       <c r="E51" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="F51" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="F51" s="34" t="s">
-        <v>68</v>
-      </c>
       <c r="G51" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I51" s="37">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="J51" s="37">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="K51" s="13">
         <v>46317</v>
@@ -4545,7 +4539,7 @@
         <v>46317</v>
       </c>
       <c r="M51" s="27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4554,28 +4548,28 @@
         <v>26</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="F52" s="34" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I52" s="37">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J52" s="37">
         <v>0.83333333333333337</v>
@@ -4587,7 +4581,7 @@
         <v>46317</v>
       </c>
       <c r="M52" s="27" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4596,25 +4590,25 @@
         <v>27</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="E53" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="F53" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="I53" s="37">
         <v>0.66666666666666663</v>
@@ -4629,10 +4623,10 @@
         <v>46317</v>
       </c>
       <c r="M53" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="26" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>28</v>
@@ -4641,22 +4635,22 @@
         <v>90</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="F54" s="34" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I54" s="37">
         <v>0.66666666666666663</v>
@@ -4671,31 +4665,31 @@
         <v>46317</v>
       </c>
       <c r="M54" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="26" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>29</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="F55" s="34" t="s">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>159</v>
@@ -4713,31 +4707,31 @@
         <v>46317</v>
       </c>
       <c r="M55" s="27" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="26" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>30</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F56" s="34" t="s">
         <v>161</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>162</v>
@@ -4755,34 +4749,34 @@
         <v>46317</v>
       </c>
       <c r="M56" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="26" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>31</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D57" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E57" s="34" t="s">
+      <c r="H57" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="F57" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="I57" s="37">
         <v>0.66666666666666663</v>
@@ -4797,34 +4791,34 @@
         <v>46317</v>
       </c>
       <c r="M57" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="26" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>32</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D58" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="F58" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="G58" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E58" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="F58" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>146</v>
-      </c>
       <c r="H58" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I58" s="37">
         <v>0.66666666666666663</v>
@@ -4839,40 +4833,40 @@
         <v>46317</v>
       </c>
       <c r="M58" s="27" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="26" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>33</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F59" s="34" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I59" s="37">
-        <v>0.66666666666666663</v>
+        <v>0</v>
       </c>
       <c r="J59" s="37">
-        <v>0.83333333333333337</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="K59" s="13">
         <v>46317</v>
@@ -4881,7 +4875,7 @@
         <v>46317</v>
       </c>
       <c r="M59" s="27" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -4890,31 +4884,31 @@
         <v>34</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C60" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H60" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D60" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>172</v>
-      </c>
       <c r="I60" s="37">
-        <v>0</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="J60" s="37">
-        <v>0.20833333333333334</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="K60" s="13">
         <v>46317</v>
@@ -4923,40 +4917,40 @@
         <v>46317</v>
       </c>
       <c r="M60" s="27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A61" s="26" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>35</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D61" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E61" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>146</v>
-      </c>
       <c r="H61" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I61" s="37">
-        <v>0.97916666666666663</v>
+        <v>0</v>
       </c>
       <c r="J61" s="37">
-        <v>0.99930555555555556</v>
+        <v>0.1875</v>
       </c>
       <c r="K61" s="13">
         <v>46317</v>
@@ -4965,7 +4959,7 @@
         <v>46317</v>
       </c>
       <c r="M61" s="27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -4974,31 +4968,31 @@
         <v>36</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C62" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H62" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E62" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="F62" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="I62" s="37">
-        <v>0</v>
+        <v>0.98611111111111116</v>
       </c>
       <c r="J62" s="37">
-        <v>0.1875</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="K62" s="13">
         <v>46317</v>
@@ -5007,40 +5001,34 @@
         <v>46317</v>
       </c>
       <c r="M62" s="27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A63" s="26" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>37</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="F63" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="G63" s="10" t="s">
-        <v>146</v>
-      </c>
+      <c r="D63" s="118" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" s="119"/>
+      <c r="F63" s="119"/>
+      <c r="G63" s="120"/>
       <c r="H63" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I63" s="37">
-        <v>0.98611111111111116</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J63" s="37">
-        <v>0.99930555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="K63" s="13">
         <v>46317</v>
@@ -5049,34 +5037,34 @@
         <v>46317</v>
       </c>
       <c r="M63" s="27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A64" s="26" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
         <v>38</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="161" t="s">
+        <v>176</v>
+      </c>
+      <c r="D64" s="118" t="s">
+        <v>177</v>
+      </c>
+      <c r="E64" s="119"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="120"/>
+      <c r="H64" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E64" s="162"/>
-      <c r="F64" s="162"/>
-      <c r="G64" s="163"/>
-      <c r="H64" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="I64" s="37">
-        <v>0.33333333333333331</v>
+        <v>0.97916666666666663</v>
       </c>
       <c r="J64" s="37">
-        <v>0.75</v>
+        <v>0.99930555555555556</v>
       </c>
       <c r="K64" s="13">
         <v>46317</v>
@@ -5085,117 +5073,97 @@
         <v>46317</v>
       </c>
       <c r="M64" s="27" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="120" x14ac:dyDescent="0.25">
-      <c r="A65" s="26" cm="1">
-        <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(_xlpm.Celda1,INDIRECT("F"&amp;ROW()-1&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda2,INDIRECT("F"&amp;ROW()-2&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda3,INDIRECT("F"&amp;ROW()-3&amp;"C"&amp;COLUMN(),FALSE),_xlpm.Celda4,INDIRECT("F"&amp;ROW()-4&amp;"C"&amp;COLUMN(),FALSE),IF(ISNUMBER(_xlpm.Celda1),_xlpm.Celda1+1,IF(ISNUMBER(_xlpm.Celda2),_xlpm.Celda2+1,IF(ISNUMBER(_xlpm.Celda3),_xlpm.Celda3+1,IF(ISNUMBER(_xlpm.Celda4),_xlpm.Celda4+1,1)))))</f>
-        <v>39</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D65" s="161" t="s">
-        <v>180</v>
-      </c>
-      <c r="E65" s="162"/>
-      <c r="F65" s="162"/>
-      <c r="G65" s="163"/>
-      <c r="H65" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="I65" s="37">
-        <v>0.97916666666666663</v>
-      </c>
-      <c r="J65" s="37">
-        <v>0.99930555555555556</v>
-      </c>
-      <c r="K65" s="13">
-        <v>46317</v>
-      </c>
-      <c r="L65" s="13">
-        <v>46317</v>
-      </c>
-      <c r="M65" s="27" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="28"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="29"/>
-    </row>
-    <row r="67" spans="1:14" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="39"/>
-      <c r="B67" s="40"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="104" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="28"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="29"/>
+    </row>
+    <row r="66" spans="1:14" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="39"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="E67" s="104"/>
-      <c r="F67" s="104"/>
-      <c r="G67" s="104"/>
-      <c r="H67" s="104"/>
-      <c r="I67" s="104"/>
-      <c r="J67" s="104"/>
-      <c r="K67" s="40"/>
-      <c r="L67" s="40"/>
-      <c r="M67" s="41"/>
-    </row>
-    <row r="68" spans="1:14" ht="140.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="69"/>
-      <c r="B68" s="154"/>
-      <c r="C68" s="154"/>
-      <c r="D68" s="154"/>
-      <c r="E68" s="154"/>
-      <c r="F68" s="154"/>
-      <c r="G68" s="154"/>
-      <c r="H68" s="154"/>
-      <c r="I68" s="70"/>
-      <c r="J68" s="70"/>
-      <c r="K68" s="70"/>
-      <c r="L68" s="70"/>
-      <c r="M68" s="71"/>
+      <c r="E66" s="110"/>
+      <c r="F66" s="110"/>
+      <c r="G66" s="110"/>
+      <c r="H66" s="110"/>
+      <c r="I66" s="110"/>
+      <c r="J66" s="110"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="41"/>
+    </row>
+    <row r="67" spans="1:14" ht="140.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="69"/>
+      <c r="B67" s="108"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="108"/>
+      <c r="E67" s="108"/>
+      <c r="F67" s="108"/>
+      <c r="G67" s="108"/>
+      <c r="H67" s="108"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
+      <c r="M67" s="71"/>
+    </row>
+    <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="109"/>
+      <c r="B68" s="109"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="109"/>
+      <c r="E68" s="109"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="109"/>
+      <c r="H68" s="109"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="57"/>
+      <c r="L68" s="57"/>
+      <c r="M68" s="57"/>
+      <c r="N68" s="67"/>
     </row>
     <row r="69" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="155"/>
-      <c r="B69" s="155"/>
-      <c r="C69" s="155"/>
-      <c r="D69" s="155"/>
-      <c r="E69" s="155"/>
-      <c r="F69" s="155"/>
-      <c r="G69" s="155"/>
-      <c r="H69" s="155"/>
-      <c r="I69" s="57"/>
-      <c r="J69" s="57"/>
-      <c r="K69" s="57"/>
-      <c r="L69" s="57"/>
-      <c r="M69" s="57"/>
+      <c r="A69" s="109"/>
+      <c r="B69" s="109"/>
+      <c r="C69" s="109"/>
+      <c r="D69" s="109"/>
+      <c r="E69" s="109"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="109"/>
+      <c r="I69" s="58"/>
+      <c r="J69" s="58"/>
+      <c r="K69" s="58"/>
+      <c r="L69" s="58"/>
+      <c r="M69" s="58"/>
       <c r="N69" s="67"/>
     </row>
     <row r="70" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="155"/>
-      <c r="B70" s="155"/>
-      <c r="C70" s="155"/>
-      <c r="D70" s="155"/>
-      <c r="E70" s="155"/>
-      <c r="F70" s="155"/>
-      <c r="G70" s="155"/>
-      <c r="H70" s="155"/>
+      <c r="A70" s="109"/>
+      <c r="B70" s="109"/>
+      <c r="C70" s="109"/>
+      <c r="D70" s="109"/>
+      <c r="E70" s="109"/>
+      <c r="F70" s="109"/>
+      <c r="G70" s="109"/>
+      <c r="H70" s="109"/>
       <c r="I70" s="58"/>
       <c r="J70" s="58"/>
       <c r="K70" s="58"/>
@@ -5203,20 +5171,20 @@
       <c r="M70" s="58"/>
       <c r="N70" s="67"/>
     </row>
-    <row r="71" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="155"/>
-      <c r="B71" s="155"/>
-      <c r="C71" s="155"/>
-      <c r="D71" s="155"/>
-      <c r="E71" s="155"/>
-      <c r="F71" s="155"/>
-      <c r="G71" s="155"/>
-      <c r="H71" s="155"/>
-      <c r="I71" s="58"/>
-      <c r="J71" s="58"/>
-      <c r="K71" s="58"/>
-      <c r="L71" s="58"/>
-      <c r="M71" s="58"/>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="67"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="67"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="67"/>
+      <c r="H71" s="67"/>
+      <c r="I71" s="67"/>
+      <c r="J71" s="67"/>
+      <c r="K71" s="67"/>
+      <c r="L71" s="67"/>
+      <c r="M71" s="67"/>
       <c r="N71" s="67"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -5251,7 +5219,7 @@
       <c r="M73" s="67"/>
       <c r="N73" s="67"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="67"/>
       <c r="B74" s="67"/>
       <c r="C74" s="67"/>
@@ -5267,44 +5235,30 @@
       <c r="M74" s="67"/>
       <c r="N74" s="67"/>
     </row>
-    <row r="75" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="67"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="68"/>
-      <c r="F75" s="68"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="67"/>
-      <c r="K75" s="67"/>
-      <c r="L75" s="67"/>
-      <c r="M75" s="67"/>
-      <c r="N75" s="67"/>
-    </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="D46:J46"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="D66:J66"/>
+    <mergeCell ref="H15:M16"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="M46:M47"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A22:A23"/>
@@ -5321,30 +5275,28 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="H15:M16"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="D45:J45"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C9:D9"/>
   </mergeCells>
-  <conditionalFormatting sqref="B24:M45">
+  <conditionalFormatting sqref="B24:M44">
     <cfRule type="expression" dxfId="4" priority="12">
       <formula>AND($K24&gt;0,$K24=$L24,$G24="TOQUE PITO")</formula>
     </cfRule>
@@ -5355,12 +5307,12 @@
       <formula>AND($K24&gt;0,$K24=$L24)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H65">
+  <conditionalFormatting sqref="H24:H64">
     <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="VENTANA DE TRABAJO BAJO COORDINACIÓN CON CONTROLADOR DE TRÁFICO">
       <formula>NOT(ISERROR(SEARCH("VENTANA DE TRABAJO BAJO COORDINACIÓN CON CONTROLADOR DE TRÁFICO",H24)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H45">
+  <conditionalFormatting sqref="H24:H44">
     <cfRule type="expression" dxfId="0" priority="11">
       <formula>AND($K24&gt;0,$K24=$L24,$G24="TOQUE PITO")</formula>
     </cfRule>
@@ -5382,14 +5334,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f45291bc-c7a1-4ef0-8ab4-c48bff5dc735" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="313609a6-81c6-46ac-ab9d-5ac73f4e1ccd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5594,27 +5544,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f45291bc-c7a1-4ef0-8ab4-c48bff5dc735" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="313609a6-81c6-46ac-ab9d-5ac73f4e1ccd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{452591B6-8C80-41FE-AFE6-A9A4EC0BE937}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E166D88B-7F68-43F4-A96E-1F45E0E93D93}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="f45291bc-c7a1-4ef0-8ab4-c48bff5dc735"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="313609a6-81c6-46ac-ab9d-5ac73f4e1ccd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5639,9 +5582,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E166D88B-7F68-43F4-A96E-1F45E0E93D93}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{452591B6-8C80-41FE-AFE6-A9A4EC0BE937}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="f45291bc-c7a1-4ef0-8ab4-c48bff5dc735"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="313609a6-81c6-46ac-ab9d-5ac73f4e1ccd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>